--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484357_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484357_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4484</v>
+        <v>4.6667</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9871</v>
+        <v>3.4299</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4613</v>
+        <v>1.2367</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6996</v>
+        <v>3.3008</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2267</v>
+        <v>-1.406</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.473</v>
+        <v>4.7069</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3861</v>
+        <v>4.1954</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5884</v>
+        <v>-1.5912</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2023</v>
+        <v>5.7866</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3135</v>
+        <v>-0.8945</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6382</v>
+        <v>0.1852</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6753</v>
+        <v>-1.0797</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>5.402</v>
+        <v>0.4161</v>
       </c>
       <c r="T2" t="n">
-        <v>4.3034</v>
+        <v>0.4067</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0986</v>
+        <v>0.0095</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9414</v>
+        <v>-0.2224</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2772</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0949</v>
+        <v>2.1991</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9944</v>
+        <v>1.9233</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1005</v>
+        <v>0.2758</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3008</v>
+        <v>1.4908</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.406</v>
+        <v>2.2597</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7069</v>
+        <v>-0.7688</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1954</v>
+        <v>2.8094</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5912</v>
+        <v>2.768</v>
       </c>
       <c r="L3" t="n">
-        <v>5.7866</v>
+        <v>0.0415</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8945</v>
+        <v>-1.3186</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1852</v>
+        <v>-0.5083</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0797</v>
+        <v>-0.8103</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1721</v>
+        <v>-4.1022</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3441</v>
+        <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1556</v>
+        <v>-0.2662</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0289</v>
+        <v>0.5016</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1267</v>
+        <v>-0.7678</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2224</v>
+        <v>2.5372</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2224</v>
+        <v>-0.1773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5628</v>
+        <v>1.2729</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5594</v>
+        <v>0.5198</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0034</v>
+        <v>0.7531</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4908</v>
+        <v>-1.6996</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2597</v>
+        <v>-1.2267</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7688</v>
+        <v>-0.473</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8094</v>
+        <v>-0.3861</v>
       </c>
       <c r="K4" t="n">
-        <v>2.768</v>
+        <v>-0.5884</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0415</v>
+        <v>0.2023</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3186</v>
+        <v>-1.3135</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5083</v>
+        <v>-0.6382</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8103</v>
+        <v>-0.6753</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9024</v>
+        <v>2.2265</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1377</v>
+        <v>1.836</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0402</v>
+        <v>0.3905</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5372</v>
+        <v>0.9414</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7145</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1773</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6726</v>
+        <v>0.2029</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4767</v>
+        <v>0.4533</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1959</v>
+        <v>-0.2503</v>
       </c>
       <c r="G5" t="n">
         <v>3.7892</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6817</v>
+        <v>-0.8062</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.2037</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9554</v>
+        <v>-1.0099</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6313</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6862</v>
+        <v>-0.4018</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6074000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2936</v>
+        <v>-0.2018</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9325</v>
+        <v>-4.0182</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2853</v>
+        <v>-3.8161</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6473</v>
+        <v>-0.2021</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6679</v>
+        <v>-2.2304</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>-2.8384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6475</v>
+        <v>0.608</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2646</v>
+        <v>-1.7878</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2648</v>
+        <v>-0.9777</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0002</v>
+        <v>-0.8101</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9861</v>
+        <v>-0.2662</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0605</v>
+        <v>0.5346</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9256</v>
+        <v>-0.8008</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2186</v>
+        <v>1.5385</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.503</v>
+        <v>-0.5579</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0288</v>
+        <v>0.7085</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4742</v>
+        <v>-1.2664</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0182</v>
+        <v>0.9325</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.8161</v>
+        <v>0.2853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2021</v>
+        <v>0.6473</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2304</v>
+        <v>0.6679</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.8384</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.608</v>
+        <v>0.6475</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7878</v>
+        <v>0.2646</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9777</v>
+        <v>0.2648</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8101</v>
+        <v>-0.0002</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3674</v>
+        <v>-0.8578</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2943</v>
+        <v>0.0406</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0731</v>
+        <v>-0.8983</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5385</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0427</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5629</v>
+        <v>-2.8052</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.904</v>
+        <v>-4.228</v>
       </c>
       <c r="F8" t="n">
-        <v>1.341</v>
+        <v>1.4227</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6249</v>
@@ -1078,13 +1078,13 @@
         <v>3.3208</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1425</v>
+        <v>-0.0998</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1833</v>
+        <v>0.8593</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0408</v>
+        <v>-0.9591</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2992</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1565</v>
+        <v>-3.1721</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4117</v>
+        <v>-1.4818</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7448</v>
+        <v>-1.6903</v>
       </c>
       <c r="G9" t="n">
         <v>0.5635</v>
@@ -1156,13 +1156,13 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8469</v>
+        <v>0.1375</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6052</v>
+        <v>0.3247</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2417</v>
+        <v>-0.1872</v>
       </c>
       <c r="V9" t="n">
         <v>-3.6778</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3375</v>
+        <v>-6.3093</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2445</v>
+        <v>-4.1346</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.093</v>
+        <v>-2.1747</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7341</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0008</v>
+        <v>1.029</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6592</v>
+        <v>0.7691</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3416</v>
+        <v>0.2599</v>
       </c>
       <c r="V10" t="n">
         <v>-3.4554</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8126</v>
+        <v>-4.9047</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9174</v>
+        <v>-3.0096</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8953</v>
+        <v>-1.8952</v>
       </c>
       <c r="G11" t="n">
-        <v>1.000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="H11" t="n">
         <v>-6.416</v>
@@ -1294,7 +1294,7 @@
         <v>13.4919</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.944099999999999</v>
+        <v>-6.9441</v>
       </c>
       <c r="N11" t="n">
         <v>-0.8682000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>16.6041</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6052000000000004</v>
+        <v>1.5129</v>
       </c>
       <c r="T11" t="n">
-        <v>4.5684</v>
+        <v>5.4763</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.9633</v>
+        <v>-3.9632</v>
       </c>
       <c r="V11" t="n">
         <v>-4.4876</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.9202</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1396</v>
+        <v>8.4207</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7806</v>
+        <v>0.8623</v>
       </c>
       <c r="G12" t="n">
         <v>2.8493</v>
@@ -1390,13 +1390,13 @@
         <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5555</v>
+        <v>0.9183</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1973</v>
+        <v>1.4783</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6418</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>4.9294</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8567</v>
+        <v>4.4873</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4827</v>
+        <v>2.9771</v>
       </c>
       <c r="F13" t="n">
-        <v>1.374</v>
+        <v>1.5102</v>
       </c>
       <c r="G13" t="n">
         <v>1.5358</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.4093</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9383</v>
+        <v>0.4327</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1597</v>
+        <v>-0.0235</v>
       </c>
       <c r="V13" t="n">
         <v>1.7609</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1392</v>
+        <v>2.7467</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1751</v>
+        <v>2.1639</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9641</v>
+        <v>0.5828</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0534</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2205</v>
+        <v>-0.172</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1558</v>
+        <v>0.1446</v>
       </c>
       <c r="U14" t="n">
-        <v>0.06469999999999999</v>
+        <v>-0.3166</v>
       </c>
       <c r="V14" t="n">
         <v>0.4326</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.2743</v>
+        <v>-0.3601</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3967</v>
+        <v>-0.1623</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1224</v>
+        <v>-0.1978</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8109</v>
+        <v>-0.4146</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2878</v>
+        <v>1.5674</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5231</v>
+        <v>-1.982</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.0004</v>
+        <v>2.1827</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2868</v>
+        <v>1.6014</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7136</v>
+        <v>0.5813</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1895</v>
+        <v>-2.5973</v>
       </c>
       <c r="N15" t="n">
-        <v>0.999</v>
+        <v>-0.034</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8095</v>
+        <v>-2.5634</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1462</v>
+        <v>-0.3315</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6382</v>
+        <v>0.2726</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.508</v>
+        <v>-0.6041</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0968</v>
+        <v>-0.786</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1219</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3588</v>
+        <v>-0.7609</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9629</v>
+        <v>-1.9922</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3958</v>
+        <v>1.2313</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4745</v>
+        <v>-1.8109</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0698</v>
+        <v>-0.2878</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4047</v>
+        <v>-1.5231</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-2.0004</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-1.2868</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.7136</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4745</v>
+        <v>0.1895</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0698</v>
+        <v>0.999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4047</v>
+        <v>-0.8095</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0925</v>
+        <v>-0.6328</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0138</v>
+        <v>-0.2337</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.399</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0968</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3796</v>
+        <v>-0.8079</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6553</v>
+        <v>-1.9475</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2757</v>
+        <v>1.1396</v>
       </c>
       <c r="G17" t="n">
         <v>-2.372</v>
@@ -1780,13 +1780,13 @@
         <v>2.7348</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6438</v>
+        <v>-0.0722</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.6364</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5725</v>
+        <v>-0.7086</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1219</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9275</v>
+        <v>-1.2304</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3757</v>
+        <v>-0.8618</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.3686</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4146</v>
+        <v>-0.4745</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5674</v>
+        <v>-0.0698</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.982</v>
+        <v>-0.4047</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1827</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6014</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5813</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5973</v>
+        <v>-0.4745</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.034</v>
+        <v>-0.0698</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5634</v>
+        <v>-0.4047</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.899</v>
+        <v>0.2208</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9408</v>
+        <v>0.1149</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9581</v>
+        <v>0.1059</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.786</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4975</v>
+        <v>-1.5118</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8099</v>
+        <v>0.121</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3124</v>
+        <v>-1.6328</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8709</v>
+        <v>1.4986</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1243</v>
+        <v>0.8918</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9953</v>
+        <v>0.6068</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3999</v>
+        <v>2.7326</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0793</v>
+        <v>0.1023</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3206</v>
+        <v>2.6303</v>
       </c>
       <c r="M19" t="n">
-        <v>0.529</v>
+        <v>-1.234</v>
       </c>
       <c r="N19" t="n">
-        <v>1.2037</v>
+        <v>0.7895</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6747</v>
+        <v>-2.0235</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0406</v>
+        <v>-0.8151</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4566</v>
+        <v>0.3186</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5839</v>
+        <v>-1.1337</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5308</v>
+        <v>-2.1475</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.789</v>
+        <v>-3.4055</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7418</v>
+        <v>1.258</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4986</v>
+        <v>-0.8709</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8918</v>
+        <v>1.1243</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6068</v>
+        <v>-1.9953</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7326</v>
+        <v>-1.3999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1023</v>
+        <v>-0.0793</v>
       </c>
       <c r="L20" t="n">
-        <v>2.6303</v>
+        <v>-1.3206</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.234</v>
+        <v>0.529</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7895</v>
+        <v>1.2037</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0235</v>
+        <v>-0.6747</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8341</v>
+        <v>-0.6906</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5915</v>
+        <v>-0.0522</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2426</v>
+        <v>-0.6384</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1352</v>
+        <v>-3.8859</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5806</v>
+        <v>-3.0862</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5546</v>
+        <v>-0.7997</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8875</v>
@@ -2092,13 +2092,13 @@
         <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3113</v>
+        <v>0.5606</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3565</v>
+        <v>0.851</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0453</v>
+        <v>-0.2904</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6056</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5.812400000000001</v>
+        <v>5.8125</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2273</v>
+        <v>2.2272</v>
       </c>
       <c r="F22" t="n">
-        <v>3.585100000000002</v>
+        <v>3.5853</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0001</v>
+        <v>-1.000100000000001</v>
       </c>
       <c r="H22" t="n">
         <v>6.4161</v>
@@ -2146,10 +2146,10 @@
         <v>6.944000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8683000000000001</v>
+        <v>0.8682999999999998</v>
       </c>
       <c r="L22" t="n">
-        <v>6.0756</v>
+        <v>6.075600000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-7.944000000000001</v>
@@ -2170,19 +2170,19 @@
         <v>19.5343</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6052</v>
+        <v>-0.6052000000000004</v>
       </c>
       <c r="T22" t="n">
         <v>3.9632</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.5685</v>
+        <v>-4.5684</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4876</v>
+        <v>4.487600000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>7.924000000000001</v>
+        <v>7.923999999999999</v>
       </c>
       <c r="X22" t="n">
         <v>-3.4367</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484357_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484357_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.2224</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1991</v>
+        <v>1.2729</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9233</v>
+        <v>0.5198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2758</v>
+        <v>0.7531</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4908</v>
+        <v>-1.6996</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2597</v>
+        <v>-1.2267</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7688</v>
+        <v>-0.473</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8094</v>
+        <v>-0.3861</v>
       </c>
       <c r="K3" t="n">
-        <v>2.768</v>
+        <v>-0.5884</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0415</v>
+        <v>0.2023</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3186</v>
+        <v>-1.3135</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5083</v>
+        <v>-0.6382</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8103</v>
+        <v>-0.6753</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2662</v>
+        <v>2.2265</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5016</v>
+        <v>1.836</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7678</v>
+        <v>0.3905</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5372</v>
+        <v>0.9414</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7145</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1773</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2729</v>
+        <v>1.221</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5198</v>
+        <v>1.221</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7531</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6996</v>
+        <v>1.221</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2267</v>
+        <v>0.614</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.473</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3861</v>
+        <v>1.221</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5884</v>
+        <v>0.614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2023</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3135</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6382</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6753</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2265</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.836</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3905</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2029</v>
+        <v>0.9781</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4533</v>
+        <v>0.7024</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2503</v>
+        <v>0.2758</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7892</v>
+        <v>0.2699</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3879</v>
+        <v>1.6457</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4013</v>
+        <v>-1.3758</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4885</v>
+        <v>1.5884</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4121</v>
+        <v>2.154</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0764</v>
+        <v>-0.5655</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6994</v>
+        <v>-1.3186</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0243</v>
+        <v>-0.5083</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6751</v>
+        <v>-0.8103</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1488</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9069</v>
+        <v>-4.1022</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8062</v>
+        <v>-0.2662</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2037</v>
+        <v>0.5016</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0099</v>
+        <v>-0.7678</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6313</v>
+        <v>2.5372</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3321</v>
+        <v>2.7145</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2992</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4018</v>
+        <v>0.2029</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>0.4533</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2018</v>
+        <v>-0.2503</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.0182</v>
+        <v>3.7892</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.8161</v>
+        <v>1.3879</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2021</v>
+        <v>2.4013</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.2304</v>
+        <v>4.4885</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.8384</v>
+        <v>1.4121</v>
       </c>
       <c r="L6" t="n">
-        <v>0.608</v>
+        <v>3.0764</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7878</v>
+        <v>-0.6994</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9777</v>
+        <v>-0.0243</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8101</v>
+        <v>-0.6751</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3441</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2662</v>
+        <v>-0.8062</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5346</v>
+        <v>0.2037</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8008</v>
+        <v>-1.0099</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5385</v>
+        <v>-0.6313</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4959</v>
+        <v>-0.3321</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0427</v>
+        <v>-0.2992</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5579</v>
+        <v>-0.4018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7085</v>
+        <v>-0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2664</v>
+        <v>-0.2018</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9325</v>
+        <v>-4.0182</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2853</v>
+        <v>-3.8161</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6473</v>
+        <v>-0.2021</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6679</v>
+        <v>-2.2304</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>-2.8384</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6475</v>
+        <v>0.608</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2646</v>
+        <v>-1.7878</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2648</v>
+        <v>-0.9777</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0002</v>
+        <v>-0.8101</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8578</v>
+        <v>-0.2662</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0406</v>
+        <v>0.5346</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8983</v>
+        <v>-0.8008</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>1.5385</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0.0427</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8052</v>
+        <v>-0.5579</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.228</v>
+        <v>0.7085</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4227</v>
+        <v>-1.2664</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6249</v>
+        <v>0.9325</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6913</v>
+        <v>0.2853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0663</v>
+        <v>0.6473</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9851</v>
+        <v>0.6679</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9968</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0116</v>
+        <v>0.6475</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6398</v>
+        <v>0.2646</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3055</v>
+        <v>0.2648</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9453</v>
+        <v>-0.0002</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3208</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0998</v>
+        <v>-0.8578</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8593</v>
+        <v>0.0406</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9591</v>
+        <v>-0.8983</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2992</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2992</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1721</v>
+        <v>-2.8052</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4818</v>
+        <v>-4.228</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6903</v>
+        <v>1.4227</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5635</v>
+        <v>-1.6249</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0916</v>
+        <v>-1.6913</v>
       </c>
       <c r="I9" t="n">
-        <v>0.472</v>
+        <v>0.0663</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0297</v>
+        <v>-0.9851</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7125</v>
+        <v>-1.9968</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7422</v>
+        <v>1.0116</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5338000000000001</v>
+        <v>-0.6398</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8041</v>
+        <v>0.3055</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2702</v>
+        <v>-0.9453</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1721</v>
+        <v>-4.1022</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>3.3208</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1375</v>
+        <v>-0.0998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3247</v>
+        <v>0.8593</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1872</v>
+        <v>-0.9591</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.6778</v>
+        <v>-0.2992</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0137</v>
+        <v>-0.2992</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3093</v>
+        <v>-3.1721</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1346</v>
+        <v>-1.4818</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1747</v>
+        <v>-1.6903</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7341</v>
+        <v>0.5635</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3004</v>
+        <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5663</v>
+        <v>0.472</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6452</v>
+        <v>0.0297</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.021</v>
+        <v>-0.7125</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3758</v>
+        <v>0.7422</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0889</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2793</v>
+        <v>0.8041</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8095</v>
+        <v>-0.2702</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>1.029</v>
+        <v>0.1375</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7691</v>
+        <v>0.3247</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2599</v>
+        <v>-0.1872</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.4554</v>
+        <v>-3.6778</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.3283</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1271</v>
+        <v>-3.0137</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9047</v>
+        <v>-6.3093</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0096</v>
+        <v>-4.1346</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8952</v>
+        <v>-2.1747</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9999999999999998</v>
+        <v>-1.7341</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.416</v>
+        <v>-2.3004</v>
       </c>
       <c r="I11" t="n">
-        <v>7.416200000000001</v>
+        <v>0.5663</v>
       </c>
       <c r="J11" t="n">
-        <v>7.944100000000001</v>
+        <v>-0.6452</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.5477</v>
+        <v>-2.021</v>
       </c>
       <c r="L11" t="n">
-        <v>13.4919</v>
+        <v>1.3758</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.9441</v>
+        <v>-1.0889</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8682000000000001</v>
+        <v>-0.2793</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.0757</v>
+        <v>-0.8095</v>
       </c>
       <c r="P11" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-19.5344</v>
-      </c>
       <c r="R11" t="n">
-        <v>16.6041</v>
+        <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5129</v>
+        <v>1.029</v>
       </c>
       <c r="T11" t="n">
-        <v>5.4763</v>
+        <v>0.7691</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.9632</v>
+        <v>0.2599</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.4876</v>
+        <v>-3.4554</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1044</v>
+        <v>-1.3283</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.591999999999999</v>
+        <v>-2.1271</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.282999999999999</v>
+        <v>-4.9047</v>
       </c>
       <c r="E12" t="n">
-        <v>8.4207</v>
+        <v>-3.0095</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8623</v>
+        <v>-1.8952</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8493</v>
+        <v>1.0001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.634</v>
+        <v>-6.416</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2154</v>
+        <v>7.4162</v>
       </c>
       <c r="J12" t="n">
-        <v>3.744</v>
+        <v>7.944100000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6398</v>
+        <v>-5.5477</v>
       </c>
       <c r="L12" t="n">
-        <v>2.1042</v>
+        <v>13.4919</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-6.944099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9942</v>
+        <v>-0.8681999999999997</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8889</v>
+        <v>-6.0757</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-19.5344</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5395</v>
+        <v>16.6041</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9183</v>
+        <v>1.5129</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4783</v>
+        <v>5.4763</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-3.9632</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9294</v>
+        <v>-4.4876</v>
       </c>
       <c r="W12" t="n">
-        <v>5.1517</v>
+        <v>3.1044</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2224</v>
-      </c>
+        <v>-7.592000000000001</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4873</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9771</v>
+        <v>8.4207</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5102</v>
+        <v>0.8623</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5358</v>
+        <v>2.8493</v>
       </c>
       <c r="H13" t="n">
-        <v>0.295</v>
+        <v>2.634</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2408</v>
+        <v>0.2154</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8066</v>
+        <v>3.744</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1049</v>
+        <v>1.6398</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7017</v>
+        <v>2.1042</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7292</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1901</v>
+        <v>0.9942</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5391</v>
+        <v>-1.8889</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4093</v>
+        <v>0.9183</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4327</v>
+        <v>1.4783</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0235</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7609</v>
+        <v>4.9294</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7145</v>
+        <v>5.1517</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9536</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7467</v>
+        <v>4.4873</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1639</v>
+        <v>2.9771</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5828</v>
+        <v>1.5102</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0534</v>
+        <v>1.5358</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4178</v>
+        <v>0.295</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3644</v>
+        <v>1.2408</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4648</v>
+        <v>0.8066</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3838</v>
+        <v>0.1049</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8486</v>
+        <v>0.7017</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5182</v>
+        <v>0.7292</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.034</v>
+        <v>0.1901</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4842</v>
+        <v>0.5391</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.172</v>
+        <v>0.4093</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1446</v>
+        <v>0.4327</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3166</v>
+        <v>-0.0235</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4326</v>
+        <v>1.7609</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>2.7145</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1219</v>
+        <v>-0.9536</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3601</v>
+        <v>2.7467</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1623</v>
+        <v>2.1639</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1978</v>
+        <v>0.5828</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4146</v>
+        <v>-0.0534</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5674</v>
+        <v>-0.4178</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.982</v>
+        <v>0.3644</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1827</v>
+        <v>1.4648</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6014</v>
+        <v>-0.3838</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5813</v>
+        <v>1.8486</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5973</v>
+        <v>-1.5182</v>
       </c>
       <c r="N15" t="n">
         <v>-0.034</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5634</v>
+        <v>-1.4842</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1255</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3315</v>
+        <v>-0.172</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2726</v>
+        <v>0.1446</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6041</v>
+        <v>-0.3166</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.786</v>
+        <v>0.4326</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6642</v>
+        <v>0.5545</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1219</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7609</v>
+        <v>-0.3601</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9922</v>
+        <v>-0.1623</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2313</v>
+        <v>-0.1978</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8109</v>
+        <v>-0.4146</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2878</v>
+        <v>1.5674</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5231</v>
+        <v>-1.982</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.0004</v>
+        <v>2.1827</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2868</v>
+        <v>1.6014</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7136</v>
+        <v>0.5813</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1895</v>
+        <v>-2.5973</v>
       </c>
       <c r="N16" t="n">
-        <v>0.999</v>
+        <v>-0.034</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8095</v>
+        <v>-2.5634</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>3.1255</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6328</v>
+        <v>-0.3315</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2337</v>
+        <v>0.2726</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.399</v>
+        <v>-0.6041</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0968</v>
+        <v>-0.786</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X16" t="n">
         <v>-0.1219</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8079</v>
+        <v>-0.7609</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9475</v>
+        <v>-1.9922</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1396</v>
+        <v>1.2313</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.372</v>
+        <v>-1.8109</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4973</v>
+        <v>-0.2878</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8746</v>
+        <v>-1.5231</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6072</v>
+        <v>-2.0004</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.7562</v>
+        <v>-1.2868</v>
       </c>
       <c r="L17" t="n">
-        <v>0.149</v>
+        <v>-0.7136</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7647</v>
+        <v>0.1895</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2589</v>
+        <v>0.999</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0237</v>
+        <v>-0.8095</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0722</v>
+        <v>-0.6328</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6364</v>
+        <v>-0.2337</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7086</v>
+        <v>-0.399</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1219</v>
+        <v>1.0968</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
         <v>-0.1219</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2304</v>
+        <v>-0.8079</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8618</v>
+        <v>-1.9475</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3686</v>
+        <v>1.1396</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4745</v>
+        <v>-2.372</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0698</v>
+        <v>-0.4973</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4047</v>
+        <v>-1.8746</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1.6072</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-1.7562</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4745</v>
+        <v>-0.7647</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0698</v>
+        <v>1.2589</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4047</v>
+        <v>-2.0237</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.7348</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2208</v>
+        <v>-0.0722</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1149</v>
+        <v>0.6364</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1059</v>
+        <v>-0.7086</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5118</v>
+        <v>-1.2304</v>
       </c>
       <c r="E19" t="n">
-        <v>0.121</v>
+        <v>-0.8618</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6328</v>
+        <v>-0.3686</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4986</v>
+        <v>-0.4745</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8918</v>
+        <v>-0.0698</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6068</v>
+        <v>-0.4047</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7326</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1023</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.6303</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.234</v>
+        <v>-0.4745</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7895</v>
+        <v>-0.0698</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0235</v>
+        <v>-0.4047</v>
       </c>
       <c r="P19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8151</v>
+        <v>0.2208</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3186</v>
+        <v>0.1149</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1337</v>
+        <v>0.1059</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1475</v>
+        <v>-1.5118</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4055</v>
+        <v>0.121</v>
       </c>
       <c r="F20" t="n">
-        <v>1.258</v>
+        <v>-1.6328</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8709</v>
+        <v>1.4986</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1243</v>
+        <v>0.8918</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9953</v>
+        <v>0.6068</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3999</v>
+        <v>2.7326</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0793</v>
+        <v>0.1023</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3206</v>
+        <v>2.6303</v>
       </c>
       <c r="M20" t="n">
-        <v>0.529</v>
+        <v>-1.234</v>
       </c>
       <c r="N20" t="n">
-        <v>1.2037</v>
+        <v>0.7895</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6747</v>
+        <v>-2.0235</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6906</v>
+        <v>-0.8151</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0522</v>
+        <v>0.3186</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6384</v>
+        <v>-1.1337</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8859</v>
+        <v>-2.1475</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0862</v>
+        <v>-3.4055</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7997</v>
+        <v>1.258</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8875</v>
+        <v>-0.8709</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1763</v>
+        <v>1.1243</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0638</v>
+        <v>-1.9953</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0208</v>
+        <v>-1.3999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.926</v>
+        <v>-0.0793</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09470000000000001</v>
+        <v>-1.3206</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9083</v>
+        <v>0.529</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2502</v>
+        <v>1.2037</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1585</v>
+        <v>-0.6747</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-3.9069</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5606</v>
+        <v>-0.6906</v>
       </c>
       <c r="T21" t="n">
-        <v>0.851</v>
+        <v>-0.0522</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2904</v>
+        <v>-0.6384</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.6056</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.0511</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,152 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-3.8859</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.0862</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.7997</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.8875</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.1763</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2.0638</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.0208</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.9083</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-2.1585</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.2904</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.6056</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-1.0511</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484357_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>5.8125</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>2.2272</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>3.5853</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>-1.000100000000001</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>6.4161</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>-7.4161</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>6.944000000000001</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>0.8682999999999998</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>6.075600000000001</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>-7.944000000000001</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>5.547799999999999</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>-13.492</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>2.930299999999999</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>-16.604</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>19.5343</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>-0.6052000000000004</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>3.9632</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>-4.5684</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V23" t="n">
         <v>4.487600000000001</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W23" t="n">
         <v>7.923999999999999</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X23" t="n">
         <v>-3.4367</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
